--- a/RECETAS_INFOREST_CARTA_Y_POSTRES.xlsx
+++ b/RECETAS_INFOREST_CARTA_Y_POSTRES.xlsx
@@ -14543,7 +14543,7 @@
         <v>1000</v>
       </c>
       <c r="L173" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M173" s="13" t="n">
         <v>20</v>
